--- a/docs/data/jp/xlsx/4968.xlsx
+++ b/docs/data/jp/xlsx/4968.xlsx
@@ -10489,7 +10489,7 @@
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>Loss On Valuation Of Noncurrent Assets EL</t>
+          <t>고정자산 평가손</t>
         </is>
       </c>
       <c r="T133" s="20" t="n">
@@ -10543,7 +10543,7 @@
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>Settlement Money EL</t>
+          <t>해결금</t>
         </is>
       </c>
       <c r="I136" s="20" t="n">
@@ -15703,7 +15703,7 @@
     <row r="227">
       <c r="A227" s="18" t="inlineStr">
         <is>
-          <t>Amortization Of Business Commencement Expenses Ope CF</t>
+          <t>개업비 상각액</t>
         </is>
       </c>
       <c r="C227" s="20" t="n">
@@ -16123,7 +16123,7 @@
     <row r="233">
       <c r="A233" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Loss On Business Liquidation Ope CF</t>
+          <t>사업 정리 손실 충당금 증감액(△는 감소)</t>
         </is>
       </c>
       <c r="C233" s="20" t="n">
@@ -16264,7 +16264,7 @@
     <row r="236">
       <c r="A236" s="18" t="inlineStr">
         <is>
-          <t>Loss On Valuation Of Noncurrent Assets Ope CF</t>
+          <t>고정자산 평가손</t>
         </is>
       </c>
       <c r="E236" s="20" t="n">
@@ -16449,7 +16449,7 @@
     <row r="241">
       <c r="A241" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Sales Of Investments In Capital Ope CF</t>
+          <t>출자금 매각 손익(△는 이익)</t>
         </is>
       </c>
       <c r="Q241" s="20" t="n">
@@ -16465,7 +16465,7 @@
     <row r="242">
       <c r="A242" s="18" t="inlineStr">
         <is>
-          <t>Loss On Valuation Of Investments In Capital Ope CF</t>
+          <t>출자금 평가손</t>
         </is>
       </c>
       <c r="R242" s="20" t="n">
@@ -16503,7 +16503,7 @@
     <row r="244">
       <c r="A244" s="18" t="inlineStr">
         <is>
-          <t>Loss On Explosion And Fire Ope CF</t>
+          <t>폭발 화재 사고 손실</t>
         </is>
       </c>
       <c r="O244" s="20" t="n">
@@ -16519,7 +16519,7 @@
     <row r="245">
       <c r="A245" s="18" t="inlineStr">
         <is>
-          <t>Loss On Liquidation Of Business For Subsidiaries Ope CF</t>
+          <t>관계회사 사업 정리 손실</t>
         </is>
       </c>
       <c r="O245" s="20" t="n">
@@ -16586,7 +16586,7 @@
     <row r="249">
       <c r="A249" s="18" t="inlineStr">
         <is>
-          <t>Settlement Money Ope CF</t>
+          <t>해결금</t>
         </is>
       </c>
       <c r="H249" s="20" t="n">
@@ -17444,7 +17444,7 @@
     <row r="264">
       <c r="A264" s="18" t="inlineStr">
         <is>
-          <t>Settlement Money Paid Ope CF</t>
+          <t>해결금 지급액</t>
         </is>
       </c>
       <c r="H264" s="20" t="n">
@@ -18107,7 +18107,7 @@
     <row r="276">
       <c r="A276" s="18" t="inlineStr">
         <is>
-          <t>Payments For Deferred Assets Inv CF</t>
+          <t>이연자산 취득 지출</t>
         </is>
       </c>
       <c r="C276" s="20" t="n">
